--- a/diseases/d085/2005-2009.xlsx
+++ b/diseases/d085/2005-2009.xlsx
@@ -15012,6 +15012,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16340,6 +16345,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24824,6 +24834,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26152,6 +26167,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34082,6 +34102,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34466,6 +34491,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35322,6 +35352,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35706,6 +35741,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36562,6 +36602,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36944,6 +36989,11 @@
       <c r="S176" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">

--- a/diseases/d085/2005-2009.xlsx
+++ b/diseases/d085/2005-2009.xlsx
@@ -14208,11 +14208,6 @@
       <c r="R97" t="n">
         <v>0.09929710064878244</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U97" t="inlineStr">
         <is>
           <t>SER_SI_ECDC_TOXO_ANNUAL</t>
@@ -14230,12 +14225,7 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ97" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
@@ -14245,11 +14235,6 @@
       </c>
       <c r="AT97" t="n">
         <v>1</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -14315,17 +14300,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -14364,34 +14349,12 @@
       <c r="O98" t="n">
         <v>2</v>
       </c>
+      <c r="R98" t="n">
+        <v>0.03719546907113057</v>
+      </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis, congenital</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -14399,64 +14362,6 @@
           <t>annual</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD98" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE98" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF98" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG98" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN98" t="b">
-        <v>1</v>
-      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -14464,27 +14369,17 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ98" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT98" t="n">
         <v>1</v>
       </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV98" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -14492,7 +14387,7 @@
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
@@ -14512,7 +14407,7 @@
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
@@ -14554,12 +14449,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -14584,7 +14479,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2007-01-08</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -14593,22 +14488,19 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O99" t="n">
-        <v>2</v>
-      </c>
-      <c r="R99" t="n">
-        <v>0.03719546907113057</v>
+        <v>1</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -14623,7 +14515,7 @@
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
         </is>
       </c>
       <c r="AT99" t="n">
@@ -14631,42 +14523,42 @@
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -14728,7 +14620,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2007-01-08</t>
+          <t>2007-01-15</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -14869,7 +14761,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2007-01-15</t>
+          <t>2007-01-22</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -15010,7 +14902,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2007-01-22</t>
+          <t>2007-01-29</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -15019,10 +14911,10 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
@@ -15151,19 +15043,19 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2007-01-29</t>
+          <t>2007-02-05</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2007-02</t>
         </is>
       </c>
       <c r="N103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -15292,7 +15184,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2007-02-05</t>
+          <t>2007-02-12</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -15433,7 +15325,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2007-02-12</t>
+          <t>2007-02-26</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -15442,10 +15334,10 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
@@ -15574,19 +15466,19 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2007-02-26</t>
+          <t>2007-03-12</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2007-02</t>
+          <t>2007-03</t>
         </is>
       </c>
       <c r="N106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U106" t="inlineStr">
         <is>
@@ -15715,7 +15607,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2007-03-12</t>
+          <t>2007-03-19</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -15856,7 +15748,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2007-03-19</t>
+          <t>2007-03-26</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -15997,12 +15889,12 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2007-03-26</t>
+          <t>2007-04-09</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2007-03</t>
+          <t>2007-04</t>
         </is>
       </c>
       <c r="N109" t="n">
@@ -16138,7 +16030,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2007-04-09</t>
+          <t>2007-04-16</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -16279,7 +16171,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2007-04-16</t>
+          <t>2007-04-23</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -16288,10 +16180,10 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
@@ -16420,7 +16312,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2007-04-23</t>
+          <t>2007-04-30</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -16429,10 +16321,10 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
@@ -16561,19 +16453,19 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2007-04-30</t>
+          <t>2007-05-07</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2007-04</t>
+          <t>2007-05</t>
         </is>
       </c>
       <c r="N113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
@@ -16702,7 +16594,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2007-05-07</t>
+          <t>2007-05-14</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -16711,10 +16603,10 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
@@ -16843,19 +16735,19 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2007-05-14</t>
+          <t>2007-06-11</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2007-05</t>
+          <t>2007-06</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
@@ -16984,7 +16876,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2007-06-11</t>
+          <t>2007-06-18</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -17095,12 +16987,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -17125,33 +17017,34 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2007-06-18</t>
+          <t>2007-07-01</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2007-06</t>
+          <t>2007-07</t>
         </is>
       </c>
       <c r="N117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O117" t="n">
-        <v>2</v>
-      </c>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.004346517596181046</v>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
@@ -17159,52 +17052,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS117" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
+      <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17236,12 +17125,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -17266,7 +17155,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2007-07-01</t>
+          <t>2007-07-02</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -17280,20 +17169,19 @@
       <c r="O118" t="n">
         <v>1</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" t="n">
-        <v>0.004346517596181046</v>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
@@ -17301,48 +17189,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS118" t="inlineStr"/>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
       <c r="AT118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -17404,7 +17296,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2007-07-02</t>
+          <t>2007-07-09</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -17413,10 +17305,10 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
@@ -17545,7 +17437,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2007-07-09</t>
+          <t>2007-07-30</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -17554,10 +17446,10 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
@@ -17686,12 +17578,12 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2007-07-30</t>
+          <t>2007-08-13</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2007-07</t>
+          <t>2007-08</t>
         </is>
       </c>
       <c r="N121" t="n">
@@ -17827,7 +17719,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2007-08-13</t>
+          <t>2007-08-20</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -17968,7 +17860,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2007-08-20</t>
+          <t>2007-08-27</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -17977,10 +17869,10 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U123" t="inlineStr">
         <is>
@@ -18109,19 +18001,19 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2007-08-27</t>
+          <t>2007-09-10</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>2007-08</t>
+          <t>2007-09</t>
         </is>
       </c>
       <c r="N124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
@@ -18250,7 +18142,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2007-09-10</t>
+          <t>2007-09-24</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -18391,12 +18283,12 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2007-09-24</t>
+          <t>2007-10-08</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2007-09</t>
+          <t>2007-10</t>
         </is>
       </c>
       <c r="N126" t="n">
@@ -18532,7 +18424,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2007-10-08</t>
+          <t>2007-10-15</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -18541,10 +18433,10 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
@@ -18673,7 +18565,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2007-10-15</t>
+          <t>2007-10-29</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -18682,10 +18574,10 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U128" t="inlineStr">
         <is>
@@ -18814,12 +18706,12 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2007-10-29</t>
+          <t>2007-11-05</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>2007-10</t>
+          <t>2007-11</t>
         </is>
       </c>
       <c r="N129" t="n">
@@ -18955,7 +18847,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2007-11-05</t>
+          <t>2007-11-19</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -19096,7 +18988,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2007-11-19</t>
+          <t>2007-11-26</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -19105,10 +18997,10 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U131" t="inlineStr">
         <is>
@@ -19207,12 +19099,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -19237,33 +19129,34 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2007-11-26</t>
+          <t>2007-12-01</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2007-11</t>
+          <t>2007-12</t>
         </is>
       </c>
       <c r="N132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O132" t="n">
-        <v>2</v>
-      </c>
-      <c r="U132" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.004346517596181046</v>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
@@ -19271,52 +19164,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS132" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
+      <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -19348,12 +19237,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -19378,7 +19267,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-12-03</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -19387,25 +19276,24 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O133" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
-      <c r="R133" t="n">
-        <v>0.004346517596181046</v>
+        <v>2</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
@@ -19413,48 +19301,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS133" t="inlineStr"/>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
       <c r="AT133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19486,12 +19378,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -19516,28 +19408,31 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2007-12-03</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2007-12</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O134" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.03981107521552887</v>
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+          <t>SER_BG_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -19552,7 +19447,7 @@
       </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+          <t>SER_BG_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT134" t="n">
@@ -19560,42 +19455,42 @@
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -19627,12 +19522,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -19666,17 +19561,17 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>0.03981107521552887</v>
+        <v>0</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>SER_BG_ECDC_TOXO_ANNUAL</t>
+          <t>SER_CY_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -19696,7 +19591,7 @@
       </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>SER_BG_ECDC_TOXO_ANNUAL</t>
+          <t>SER_CY_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT135" t="n">
@@ -19709,7 +19604,7 @@
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
@@ -19729,7 +19624,7 @@
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
@@ -19771,12 +19666,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -19810,17 +19705,17 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>0.01927099279578023</v>
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_TOXO_ANNUAL</t>
+          <t>SER_CZ_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -19840,7 +19735,7 @@
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_TOXO_ANNUAL</t>
+          <t>SER_CZ_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT136" t="n">
@@ -19853,7 +19748,7 @@
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
@@ -19873,7 +19768,7 @@
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
@@ -19915,12 +19810,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -19954,17 +19849,17 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>0.01927099279578023</v>
+        <v>0</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_TOXO_ANNUAL</t>
+          <t>SER_EE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -19984,7 +19879,7 @@
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_TOXO_ANNUAL</t>
+          <t>SER_EE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT137" t="n">
@@ -19997,7 +19892,7 @@
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
@@ -20017,7 +19912,7 @@
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
@@ -20059,12 +19954,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -20098,17 +19993,17 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>0.00216286110534228</v>
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_TOXO_ANNUAL</t>
+          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -20128,7 +20023,7 @@
       </c>
       <c r="AS138" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_TOXO_ANNUAL</t>
+          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT138" t="n">
@@ -20141,7 +20036,7 @@
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
@@ -20161,7 +20056,7 @@
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
@@ -20203,12 +20098,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -20242,17 +20137,17 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>0.00216286110534228</v>
+        <v>0</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
+          <t>SER_FI_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -20272,7 +20167,7 @@
       </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
+          <t>SER_FI_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT139" t="n">
@@ -20280,42 +20175,42 @@
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20347,12 +20242,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -20386,17 +20281,17 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O140" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>0.00806096585864163</v>
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_TOXO_ANNUAL</t>
+          <t>SER_GB_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -20416,7 +20311,7 @@
       </c>
       <c r="AS140" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_TOXO_ANNUAL</t>
+          <t>SER_GB_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT140" t="n">
@@ -20424,42 +20319,42 @@
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -20491,12 +20386,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -20530,17 +20425,17 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O141" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R141" t="n">
-        <v>0.00806096585864163</v>
+        <v>0.009983370699425965</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_TOXO_ANNUAL</t>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -20560,7 +20455,7 @@
       </c>
       <c r="AS141" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_TOXO_ANNUAL</t>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT141" t="n">
@@ -20573,7 +20468,7 @@
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
@@ -20593,7 +20488,7 @@
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
@@ -20635,12 +20530,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -20674,17 +20569,17 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R142" t="n">
-        <v>0.009983370699425965</v>
+        <v>0.04458315253936163</v>
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_IE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -20704,7 +20599,7 @@
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_IE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT142" t="n">
@@ -20712,42 +20607,42 @@
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
     </row>
@@ -20779,12 +20674,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -20818,17 +20713,17 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>0.04458315253936163</v>
+        <v>0</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -20848,7 +20743,7 @@
       </c>
       <c r="AS143" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT143" t="n">
@@ -20856,42 +20751,42 @@
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -20923,12 +20818,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -20972,7 +20867,7 @@
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -20992,7 +20887,7 @@
       </c>
       <c r="AS144" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT144" t="n">
@@ -21005,7 +20900,7 @@
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
@@ -21025,7 +20920,7 @@
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
@@ -21067,12 +20962,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -21116,7 +21011,7 @@
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -21136,7 +21031,7 @@
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT145" t="n">
@@ -21149,7 +21044,7 @@
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
@@ -21169,7 +21064,7 @@
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
@@ -21211,12 +21106,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -21260,7 +21155,7 @@
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
+          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -21280,7 +21175,7 @@
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
+          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT146" t="n">
@@ -21293,7 +21188,7 @@
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
@@ -21313,7 +21208,7 @@
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
@@ -21355,12 +21250,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -21394,17 +21289,17 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O147" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>0.02105490218392499</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -21424,7 +21319,7 @@
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT147" t="n">
@@ -21437,7 +21332,7 @@
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
@@ -21457,7 +21352,7 @@
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
@@ -21499,12 +21394,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -21538,17 +21433,17 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>0.02105490218392499</v>
+        <v>0</v>
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -21568,7 +21463,7 @@
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT148" t="n">
@@ -21581,7 +21476,7 @@
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
@@ -21601,7 +21496,7 @@
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
@@ -21643,12 +21538,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -21692,7 +21587,7 @@
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -21712,7 +21607,7 @@
       </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT149" t="n">
@@ -21725,7 +21620,7 @@
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
@@ -21745,7 +21640,7 @@
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
@@ -21787,12 +21682,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -21834,14 +21729,9 @@
       <c r="R150" t="n">
         <v>0</v>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -21856,27 +21746,17 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ150" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT150" t="n">
         <v>1</v>
       </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV150" t="inlineStr">
         <is>
           <t>ecdc_atlas_annual</t>
@@ -21884,7 +21764,7 @@
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
@@ -21904,7 +21784,7 @@
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
@@ -21941,17 +21821,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -21976,7 +21856,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2008-01-07</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -21985,103 +21865,20 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V151" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W151" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis, congenital</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD151" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE151" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF151" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG151" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN151" t="b">
-        <v>1</v>
+          <t>unknown</t>
+        </is>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
@@ -22090,65 +21887,55 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ151" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
         </is>
       </c>
       <c r="AT151" t="n">
         <v>1</v>
       </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22180,12 +21967,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -22210,7 +21997,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2008-01-21</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -22219,22 +22006,19 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O152" t="n">
-        <v>0</v>
-      </c>
-      <c r="R152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -22249,7 +22033,7 @@
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
         </is>
       </c>
       <c r="AT152" t="n">
@@ -22257,42 +22041,42 @@
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22354,7 +22138,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2008-01-07</t>
+          <t>2008-01-28</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -22363,10 +22147,10 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U153" t="inlineStr">
         <is>
@@ -22495,19 +22279,19 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2008-01-21</t>
+          <t>2008-02-04</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="N154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
@@ -22636,19 +22420,19 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2008-01-28</t>
+          <t>2008-02-11</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="N155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U155" t="inlineStr">
         <is>
@@ -22777,7 +22561,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2008-02-04</t>
+          <t>2008-02-18</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -22786,10 +22570,10 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U156" t="inlineStr">
         <is>
@@ -22918,7 +22702,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2008-02-11</t>
+          <t>2008-02-25</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -23059,12 +22843,12 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2008-02-18</t>
+          <t>2008-03-24</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2008-03</t>
         </is>
       </c>
       <c r="N158" t="n">
@@ -23200,19 +22984,19 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2008-02-25</t>
+          <t>2008-03-31</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2008-03</t>
         </is>
       </c>
       <c r="N159" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O159" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U159" t="inlineStr">
         <is>
@@ -23341,12 +23125,12 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2008-03-24</t>
+          <t>2008-04-14</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2008-03</t>
+          <t>2008-04</t>
         </is>
       </c>
       <c r="N160" t="n">
@@ -23482,19 +23266,19 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2008-03-31</t>
+          <t>2008-04-21</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2008-03</t>
+          <t>2008-04</t>
         </is>
       </c>
       <c r="N161" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O161" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U161" t="inlineStr">
         <is>
@@ -23623,7 +23407,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2008-04-14</t>
+          <t>2008-04-28</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -23764,19 +23548,19 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2008-04-21</t>
+          <t>2008-05-05</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2008-04</t>
+          <t>2008-05</t>
         </is>
       </c>
       <c r="N163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U163" t="inlineStr">
         <is>
@@ -23905,19 +23689,19 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2008-04-28</t>
+          <t>2008-05-12</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2008-04</t>
+          <t>2008-05</t>
         </is>
       </c>
       <c r="N164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U164" t="inlineStr">
         <is>
@@ -24046,7 +23830,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2008-05-05</t>
+          <t>2008-05-19</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -24187,7 +23971,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2008-05-12</t>
+          <t>2008-05-26</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -24196,10 +23980,10 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U166" t="inlineStr">
         <is>
@@ -24298,12 +24082,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -24328,12 +24112,12 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2008-05-19</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2008-05</t>
+          <t>2008-06</t>
         </is>
       </c>
       <c r="N167" t="n">
@@ -24342,19 +24126,20 @@
       <c r="O167" t="n">
         <v>1</v>
       </c>
-      <c r="U167" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
+      <c r="Q167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0.004331584715899372</v>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
@@ -24362,52 +24147,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS167" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
+      <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -24469,12 +24250,12 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2008-05-26</t>
+          <t>2008-06-16</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>2008-05</t>
+          <t>2008-06</t>
         </is>
       </c>
       <c r="N168" t="n">
@@ -24580,12 +24361,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -24610,7 +24391,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2008-06-30</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -24624,20 +24405,19 @@
       <c r="O169" t="n">
         <v>1</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
-      <c r="R169" t="n">
-        <v>0.004331584715899372</v>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
@@ -24645,48 +24425,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS169" t="inlineStr"/>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
       <c r="AT169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24748,12 +24532,12 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2008-06-16</t>
+          <t>2008-07-07</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>2008-06</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N170" t="n">
@@ -24889,12 +24673,12 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2008-06-30</t>
+          <t>2008-07-14</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2008-06</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N171" t="n">
@@ -25030,7 +24814,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2008-07-07</t>
+          <t>2008-07-21</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -25039,10 +24823,10 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U172" t="inlineStr">
         <is>
@@ -25171,7 +24955,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2008-07-14</t>
+          <t>2008-07-28</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -25180,10 +24964,10 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U173" t="inlineStr">
         <is>
@@ -25312,19 +25096,19 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2008-07-21</t>
+          <t>2008-08-25</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O174" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U174" t="inlineStr">
         <is>
@@ -25453,12 +25237,12 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2008-07-28</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N175" t="n">
@@ -25594,19 +25378,19 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2008-08-25</t>
+          <t>2008-09-22</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U176" t="inlineStr">
         <is>
@@ -25735,19 +25519,19 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-10-13</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U177" t="inlineStr">
         <is>
@@ -25846,12 +25630,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -25876,12 +25660,12 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2008-09-22</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N178" t="n">
@@ -25890,19 +25674,20 @@
       <c r="O178" t="n">
         <v>2</v>
       </c>
-      <c r="U178" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
+      <c r="Q178" t="n">
+        <v>0</v>
+      </c>
+      <c r="R178" t="n">
+        <v>0.008663169431798744</v>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
@@ -25910,52 +25695,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS178" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
+      <c r="AS178" t="inlineStr"/>
       <c r="AT178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -26017,19 +25798,19 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2008-10-13</t>
+          <t>2008-11-03</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U179" t="inlineStr">
         <is>
@@ -26128,12 +25909,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -26158,7 +25939,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-11-10</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -26167,25 +25948,24 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O180" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
-      <c r="R180" t="n">
-        <v>0.008663169431798744</v>
+        <v>1</v>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
@@ -26193,48 +25973,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS180" t="inlineStr"/>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
       <c r="AT180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26296,7 +26080,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2008-11-03</t>
+          <t>2008-11-17</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -26305,10 +26089,10 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U181" t="inlineStr">
         <is>
@@ -26437,12 +26221,12 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2008-11-10</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N182" t="n">
@@ -26578,12 +26362,12 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2008-11-17</t>
+          <t>2008-12-08</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N183" t="n">
@@ -26719,7 +26503,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-12-29</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -26830,12 +26614,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -26860,28 +26644,31 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2008-12-08</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R185" t="n">
+        <v>0</v>
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+          <t>SER_BG_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
@@ -26896,7 +26683,7 @@
       </c>
       <c r="AS185" t="inlineStr">
         <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+          <t>SER_BG_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT185" t="n">
@@ -26904,42 +26691,42 @@
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -26971,12 +26758,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -27001,28 +26788,31 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2008-12-29</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O186" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R186" t="n">
+        <v>0</v>
       </c>
       <c r="U186" t="inlineStr">
         <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+          <t>SER_CY_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>annual</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
@@ -27037,7 +26827,7 @@
       </c>
       <c r="AS186" t="inlineStr">
         <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+          <t>SER_CY_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT186" t="n">
@@ -27045,42 +26835,42 @@
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -27112,12 +26902,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -27151,17 +26941,17 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O187" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R187" t="n">
-        <v>0</v>
+        <v>0.01919204466718092</v>
       </c>
       <c r="U187" t="inlineStr">
         <is>
-          <t>SER_BG_ECDC_TOXO_ANNUAL</t>
+          <t>SER_CZ_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -27181,7 +26971,7 @@
       </c>
       <c r="AS187" t="inlineStr">
         <is>
-          <t>SER_BG_ECDC_TOXO_ANNUAL</t>
+          <t>SER_CZ_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT187" t="n">
@@ -27194,7 +26984,7 @@
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
@@ -27214,7 +27004,7 @@
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Bulgaria Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
@@ -27256,12 +27046,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -27305,7 +27095,7 @@
       </c>
       <c r="U188" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_TOXO_ANNUAL</t>
+          <t>SER_EE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -27325,7 +27115,7 @@
       </c>
       <c r="AS188" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_TOXO_ANNUAL</t>
+          <t>SER_EE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT188" t="n">
@@ -27338,7 +27128,7 @@
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
@@ -27358,7 +27148,7 @@
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
@@ -27400,12 +27190,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -27439,17 +27229,17 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R189" t="n">
-        <v>0.01919204466718092</v>
+        <v>0.00214430393535524</v>
       </c>
       <c r="U189" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_TOXO_ANNUAL</t>
+          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -27469,7 +27259,7 @@
       </c>
       <c r="AS189" t="inlineStr">
         <is>
-          <t>SER_CZ_ECDC_TOXO_ANNUAL</t>
+          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT189" t="n">
@@ -27482,7 +27272,7 @@
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
@@ -27502,7 +27292,7 @@
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Czechia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
@@ -27544,12 +27334,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -27593,7 +27383,7 @@
       </c>
       <c r="U190" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_TOXO_ANNUAL</t>
+          <t>SER_FI_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -27613,7 +27403,7 @@
       </c>
       <c r="AS190" t="inlineStr">
         <is>
-          <t>SER_EE_ECDC_TOXO_ANNUAL</t>
+          <t>SER_FI_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT190" t="n">
@@ -27621,42 +27411,42 @@
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Estonia Annual Baseline</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27688,12 +27478,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -27727,17 +27517,17 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>1</v>
+        <v>266</v>
       </c>
       <c r="O191" t="n">
-        <v>1</v>
+        <v>266</v>
       </c>
       <c r="R191" t="n">
-        <v>0.00214430393535524</v>
+        <v>0.4215099172964265</v>
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -27757,7 +27547,7 @@
       </c>
       <c r="AS191" t="inlineStr">
         <is>
-          <t>SER_ES_ECDC_TOXO_ANNUAL</t>
+          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT191" t="n">
@@ -27770,7 +27560,7 @@
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
@@ -27790,7 +27580,7 @@
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Spain Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
@@ -27832,12 +27622,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -27871,17 +27661,17 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O192" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R192" t="n">
-        <v>0</v>
+        <v>0.01599840643073225</v>
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_TOXO_ANNUAL</t>
+          <t>SER_GB_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -27901,7 +27691,7 @@
       </c>
       <c r="AS192" t="inlineStr">
         <is>
-          <t>SER_FI_ECDC_TOXO_ANNUAL</t>
+          <t>SER_GB_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT192" t="n">
@@ -27909,42 +27699,42 @@
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -27976,12 +27766,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -28015,17 +27805,17 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>266</v>
+        <v>3</v>
       </c>
       <c r="O193" t="n">
-        <v>266</v>
+        <v>3</v>
       </c>
       <c r="R193" t="n">
-        <v>0.4215099172964265</v>
+        <v>0.02999586656958671</v>
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -28045,7 +27835,7 @@
       </c>
       <c r="AS193" t="inlineStr">
         <is>
-          <t>SER_FR_ECDC_TOXO_ANNUAL</t>
+          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT193" t="n">
@@ -28058,7 +27848,7 @@
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
@@ -28078,7 +27868,7 @@
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — France Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
@@ -28120,12 +27910,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -28159,17 +27949,17 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O194" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>0.01599840643073225</v>
+        <v>0</v>
       </c>
       <c r="U194" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_TOXO_ANNUAL</t>
+          <t>SER_IE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -28189,7 +27979,7 @@
       </c>
       <c r="AS194" t="inlineStr">
         <is>
-          <t>SER_GB_ECDC_TOXO_ANNUAL</t>
+          <t>SER_IE_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT194" t="n">
@@ -28197,42 +27987,42 @@
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>hpsc_ndh</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://notifiabledisease.hpsc.ie/</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>official_arcgis_feature_service</t>
         </is>
       </c>
     </row>
@@ -28264,12 +28054,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -28303,17 +28093,17 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O195" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>0.02999586656958671</v>
+        <v>0</v>
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -28333,7 +28123,7 @@
       </c>
       <c r="AS195" t="inlineStr">
         <is>
-          <t>SER_HU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT195" t="n">
@@ -28346,7 +28136,7 @@
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
@@ -28366,7 +28156,7 @@
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
@@ -28408,12 +28198,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -28457,7 +28247,7 @@
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -28477,7 +28267,7 @@
       </c>
       <c r="AS196" t="inlineStr">
         <is>
-          <t>SER_IE_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT196" t="n">
@@ -28485,42 +28275,42 @@
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>hpsc_ndh</t>
+          <t>ecdc_atlas_annual</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>Ireland HPSC Notifiable Diseases Hub</t>
+          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://notifiabledisease.hpsc.ie/</t>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>official_arcgis_feature_service</t>
+          <t>official_ecdc_rest_aggregate</t>
         </is>
       </c>
     </row>
@@ -28552,12 +28342,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -28601,7 +28391,7 @@
       </c>
       <c r="U197" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -28621,7 +28411,7 @@
       </c>
       <c r="AS197" t="inlineStr">
         <is>
-          <t>SER_LT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT197" t="n">
@@ -28634,7 +28424,7 @@
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
@@ -28654,7 +28444,7 @@
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Lithuania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
@@ -28696,12 +28486,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -28745,7 +28535,7 @@
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -28765,7 +28555,7 @@
       </c>
       <c r="AS198" t="inlineStr">
         <is>
-          <t>SER_LU_ECDC_TOXO_ANNUAL</t>
+          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT198" t="n">
@@ -28778,7 +28568,7 @@
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
@@ -28798,7 +28588,7 @@
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Luxembourg Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
@@ -28840,12 +28630,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -28879,17 +28669,17 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O199" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R199" t="n">
-        <v>0</v>
+        <v>0.007894289152812518</v>
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -28909,7 +28699,7 @@
       </c>
       <c r="AS199" t="inlineStr">
         <is>
-          <t>SER_LV_ECDC_TOXO_ANNUAL</t>
+          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT199" t="n">
@@ -28922,7 +28712,7 @@
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
@@ -28942,7 +28732,7 @@
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
@@ -28984,12 +28774,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -29023,17 +28813,17 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O200" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R200" t="n">
-        <v>0</v>
+        <v>0.009719624551314794</v>
       </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -29053,7 +28843,7 @@
       </c>
       <c r="AS200" t="inlineStr">
         <is>
-          <t>SER_MT_ECDC_TOXO_ANNUAL</t>
+          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT200" t="n">
@@ -29066,7 +28856,7 @@
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
@@ -29086,7 +28876,7 @@
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Malta Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
@@ -29128,12 +28918,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -29167,17 +28957,17 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O201" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R201" t="n">
-        <v>0.007894289152812518</v>
+        <v>0.04912537187906513</v>
       </c>
       <c r="U201" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -29197,7 +28987,7 @@
       </c>
       <c r="AS201" t="inlineStr">
         <is>
-          <t>SER_PL_ECDC_TOXO_ANNUAL</t>
+          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT201" t="n">
@@ -29210,7 +29000,7 @@
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
@@ -29230,7 +29020,7 @@
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Poland Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
@@ -29272,12 +29062,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -29311,17 +29101,17 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O202" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R202" t="n">
-        <v>0.009719624551314794</v>
+        <v>0</v>
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -29341,7 +29131,7 @@
       </c>
       <c r="AS202" t="inlineStr">
         <is>
-          <t>SER_RO_ECDC_TOXO_ANNUAL</t>
+          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
         </is>
       </c>
       <c r="AT202" t="n">
@@ -29354,7 +29144,7 @@
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
@@ -29374,7 +29164,7 @@
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Romania Annual Baseline</t>
+          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
@@ -29416,12 +29206,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -29446,7 +29236,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2009-01-12</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -29460,22 +29250,14 @@
       <c r="O203" t="n">
         <v>1</v>
       </c>
-      <c r="R203" t="n">
-        <v>0.04912537187906513</v>
-      </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO203" t="inlineStr">
@@ -29485,65 +29267,55 @@
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ203" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS203" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
         </is>
       </c>
       <c r="AT203" t="n">
         <v>1</v>
       </c>
-      <c r="AU203" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29570,17 +29342,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -29605,7 +29377,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2009-01-19</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -29614,103 +29386,20 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U204" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V204" t="inlineStr">
-        <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W204" t="inlineStr">
-        <is>
-          <t>SRC_SI_ECDC_ATLAS</t>
-        </is>
-      </c>
-      <c r="X204" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis, congenital</t>
-        </is>
-      </c>
-      <c r="Y204" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>country:SI:national</t>
-        </is>
-      </c>
-      <c r="AD204" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE204" t="inlineStr">
-        <is>
-          <t>narrower</t>
-        </is>
-      </c>
-      <c r="AF204" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG204" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI204" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ204" t="inlineStr">
-        <is>
-          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
-        </is>
-      </c>
-      <c r="AK204" t="inlineStr">
-        <is>
-          <t>Slovenia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
-        </is>
-      </c>
-      <c r="AM204" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN204" t="b">
-        <v>1</v>
+          <t>unknown</t>
+        </is>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
@@ -29719,65 +29408,55 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ204" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS204" t="inlineStr">
         <is>
-          <t>SER_SI_ECDC_TOXO_ANNUAL</t>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
         </is>
       </c>
       <c r="AT204" t="n">
         <v>1</v>
       </c>
-      <c r="AU204" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovenia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29809,12 +29488,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -29839,7 +29518,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2009-01-26</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -29848,22 +29527,19 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O205" t="n">
-        <v>0</v>
-      </c>
-      <c r="R205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>annual</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO205" t="inlineStr">
@@ -29878,7 +29554,7 @@
       </c>
       <c r="AS205" t="inlineStr">
         <is>
-          <t>SER_SK_ECDC_TOXO_ANNUAL</t>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
         </is>
       </c>
       <c r="AT205" t="n">
@@ -29886,42 +29562,42 @@
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>ecdc_atlas_annual</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>ECDC Surveillance Atlas — Slovakia Annual Baseline</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>official_ecdc_rest_aggregate</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29953,12 +29629,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -29983,33 +29659,34 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2009-01-12</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O206" t="n">
-        <v>1</v>
-      </c>
-      <c r="U206" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>0</v>
+      </c>
+      <c r="R206" t="n">
+        <v>0.008633952820887223</v>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
@@ -30017,52 +29694,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS206" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
+      <c r="AS206" t="inlineStr"/>
       <c r="AT206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -30124,19 +29797,19 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2009-01-19</t>
+          <t>2009-02-23</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U207" t="inlineStr">
         <is>
@@ -30235,12 +29908,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -30265,12 +29938,12 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2009-01-26</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N208" t="n">
@@ -30279,19 +29952,20 @@
       <c r="O208" t="n">
         <v>1</v>
       </c>
-      <c r="U208" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
+      <c r="Q208" t="n">
+        <v>0</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0.004316976410443612</v>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
@@ -30299,52 +29973,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS208" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
+      <c r="AS208" t="inlineStr"/>
       <c r="AT208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -30376,12 +30046,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -30406,12 +30076,12 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2009-03-02</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N209" t="n">
@@ -30420,20 +30090,19 @@
       <c r="O209" t="n">
         <v>2</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
-      <c r="R209" t="n">
-        <v>0.008633952820887223</v>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
@@ -30441,48 +30110,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS209" t="inlineStr"/>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
       <c r="AT209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB209" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC209" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30544,12 +30217,12 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2009-02-23</t>
+          <t>2009-03-09</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N210" t="n">
@@ -30655,12 +30328,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -30685,7 +30358,7 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2009-03-16</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
@@ -30694,25 +30367,24 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O211" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
-      <c r="R211" t="n">
-        <v>0.004316976410443612</v>
+        <v>4</v>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
@@ -30720,48 +30392,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS211" t="inlineStr"/>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
       <c r="AT211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30823,7 +30499,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2009-03-02</t>
+          <t>2009-03-23</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -30832,10 +30508,10 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O212" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U212" t="inlineStr">
         <is>
@@ -30964,7 +30640,7 @@
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>2009-03-09</t>
+          <t>2009-03-30</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
@@ -30973,10 +30649,10 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U213" t="inlineStr">
         <is>
@@ -31105,19 +30781,19 @@
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>2009-03-16</t>
+          <t>2009-04-06</t>
         </is>
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N214" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O214" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U214" t="inlineStr">
         <is>
@@ -31246,19 +30922,19 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2009-03-23</t>
+          <t>2009-04-20</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N215" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O215" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U215" t="inlineStr">
         <is>
@@ -31387,19 +31063,19 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2009-03-30</t>
+          <t>2009-04-27</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U216" t="inlineStr">
         <is>
@@ -31528,19 +31204,19 @@
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>2009-04-06</t>
+          <t>2009-05-04</t>
         </is>
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N217" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O217" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U217" t="inlineStr">
         <is>
@@ -31669,19 +31345,19 @@
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2009-04-20</t>
+          <t>2009-05-18</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N218" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O218" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U218" t="inlineStr">
         <is>
@@ -31810,12 +31486,12 @@
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>2009-04-27</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N219" t="n">
@@ -31921,12 +31597,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -31951,33 +31627,34 @@
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2009-05-04</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N220" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O220" t="n">
-        <v>3</v>
-      </c>
-      <c r="U220" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="Q220" t="n">
+        <v>0</v>
+      </c>
+      <c r="R220" t="n">
+        <v>0.004316976410443612</v>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
@@ -31985,52 +31662,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS220" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
+      <c r="AS220" t="inlineStr"/>
       <c r="AT220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -32092,12 +31765,12 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>2009-05-18</t>
+          <t>2009-06-08</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N221" t="n">
@@ -32233,7 +31906,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-06-22</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -32242,10 +31915,10 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O222" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U222" t="inlineStr">
         <is>
@@ -32344,12 +32017,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -32374,7 +32047,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-06-29</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -32388,20 +32061,19 @@
       <c r="O223" t="n">
         <v>1</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
-      <c r="R223" t="n">
-        <v>0.004316976410443612</v>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
@@ -32409,48 +32081,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS223" t="inlineStr"/>
+      <c r="AS223" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
       <c r="AT223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32482,12 +32158,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -32512,12 +32188,12 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>2009-06-08</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N224" t="n">
@@ -32526,19 +32202,20 @@
       <c r="O224" t="n">
         <v>1</v>
       </c>
-      <c r="U224" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
+      <c r="Q224" t="n">
+        <v>0</v>
+      </c>
+      <c r="R224" t="n">
+        <v>0.004316976410443612</v>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP224" t="inlineStr">
@@ -32546,52 +32223,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS224" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
+      <c r="AS224" t="inlineStr"/>
       <c r="AT224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -32653,19 +32326,19 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>2009-06-22</t>
+          <t>2009-07-20</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N225" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O225" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U225" t="inlineStr">
         <is>
@@ -32794,12 +32467,12 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>2009-06-29</t>
+          <t>2009-08-03</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N226" t="n">
@@ -32905,12 +32578,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -32935,12 +32608,12 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-08-10</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N227" t="n">
@@ -32949,20 +32622,19 @@
       <c r="O227" t="n">
         <v>1</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
-      <c r="R227" t="n">
-        <v>0.004316976410443612</v>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
@@ -32970,48 +32642,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS227" t="inlineStr"/>
+      <c r="AS227" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
       <c r="AT227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -33073,19 +32749,19 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>2009-07-20</t>
+          <t>2009-08-17</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-08</t>
         </is>
       </c>
       <c r="N228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U228" t="inlineStr">
         <is>
@@ -33214,7 +32890,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>2009-08-03</t>
+          <t>2009-08-24</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -33223,10 +32899,10 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U229" t="inlineStr">
         <is>
@@ -33355,19 +33031,19 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2009-08-10</t>
+          <t>2009-09-07</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U230" t="inlineStr">
         <is>
@@ -33496,12 +33172,12 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2009-08-17</t>
+          <t>2009-09-14</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N231" t="n">
@@ -33637,19 +33313,19 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>2009-08-24</t>
+          <t>2009-09-21</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-09</t>
         </is>
       </c>
       <c r="N232" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O232" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U232" t="inlineStr">
         <is>
@@ -33748,12 +33424,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -33778,33 +33454,34 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>2009-09-07</t>
+          <t>2009-10-01</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-10</t>
         </is>
       </c>
       <c r="N233" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O233" t="n">
-        <v>2</v>
-      </c>
-      <c r="U233" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>0</v>
+      </c>
+      <c r="R233" t="n">
+        <v>0.004316976410443612</v>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
@@ -33812,52 +33489,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS233" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
+      <c r="AS233" t="inlineStr"/>
       <c r="AT233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -33919,12 +33592,12 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2009-09-14</t>
+          <t>2009-10-19</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-10</t>
         </is>
       </c>
       <c r="N234" t="n">
@@ -34030,12 +33703,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -34060,12 +33733,12 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2009-09-21</t>
+          <t>2009-11-01</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-11</t>
         </is>
       </c>
       <c r="N235" t="n">
@@ -34074,19 +33747,20 @@
       <c r="O235" t="n">
         <v>1</v>
       </c>
-      <c r="U235" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
+      <c r="Q235" t="n">
+        <v>0</v>
+      </c>
+      <c r="R235" t="n">
+        <v>0.004316976410443612</v>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
@@ -34094,52 +33768,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS235" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
+      <c r="AS235" t="inlineStr"/>
       <c r="AT235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -34171,12 +33841,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -34201,34 +33871,33 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-11-09</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-11</t>
         </is>
       </c>
       <c r="N236" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O236" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
-      <c r="R236" t="n">
-        <v>0.004316976410443612</v>
+        <v>4</v>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
@@ -34236,48 +33905,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS236" t="inlineStr"/>
+      <c r="AS236" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
       <c r="AT236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34339,12 +34012,12 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>2009-10-19</t>
+          <t>2009-11-30</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-11</t>
         </is>
       </c>
       <c r="N237" t="n">
@@ -34450,12 +34123,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -34480,34 +34153,33 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-12-07</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-12</t>
         </is>
       </c>
       <c r="N238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O238" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
-      <c r="R238" t="n">
-        <v>0.004316976410443612</v>
+        <v>2</v>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
@@ -34515,48 +34187,52 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS238" t="inlineStr"/>
+      <c r="AS238" t="inlineStr">
+        <is>
+          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
+        </is>
+      </c>
       <c r="AT238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34618,19 +34294,19 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2009-11-09</t>
+          <t>2009-12-14</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-12</t>
         </is>
       </c>
       <c r="N239" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O239" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U239" t="inlineStr">
         <is>
@@ -34696,429 +34372,6 @@
         </is>
       </c>
       <c r="BC239" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>DE-SN</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>Sachsen, Germany</t>
-        </is>
-      </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="J240" t="inlineStr">
-        <is>
-          <t>弓形体病</t>
-        </is>
-      </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t>Parasitic</t>
-        </is>
-      </c>
-      <c r="L240" t="inlineStr">
-        <is>
-          <t>2009-11-30</t>
-        </is>
-      </c>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>2009-11</t>
-        </is>
-      </c>
-      <c r="N240" t="n">
-        <v>1</v>
-      </c>
-      <c r="O240" t="n">
-        <v>1</v>
-      </c>
-      <c r="U240" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
-      <c r="AA240" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO240" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP240" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
-      <c r="AT240" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV240" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW240" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX240" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY240" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ240" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA240" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB240" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC240" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>DE-SN</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>Sachsen, Germany</t>
-        </is>
-      </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="J241" t="inlineStr">
-        <is>
-          <t>弓形体病</t>
-        </is>
-      </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t>Parasitic</t>
-        </is>
-      </c>
-      <c r="L241" t="inlineStr">
-        <is>
-          <t>2009-12-07</t>
-        </is>
-      </c>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>2009-12</t>
-        </is>
-      </c>
-      <c r="N241" t="n">
-        <v>2</v>
-      </c>
-      <c r="O241" t="n">
-        <v>2</v>
-      </c>
-      <c r="U241" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
-      <c r="AA241" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO241" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP241" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS241" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
-      <c r="AT241" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV241" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW241" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX241" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY241" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ241" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA241" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB241" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC241" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>DE-SN</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>Sachsen, Germany</t>
-        </is>
-      </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>D085</t>
-        </is>
-      </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>Toxoplasmosis</t>
-        </is>
-      </c>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t>弓形体病</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t>Parasitic</t>
-        </is>
-      </c>
-      <c r="L242" t="inlineStr">
-        <is>
-          <t>2009-12-14</t>
-        </is>
-      </c>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>2009-12</t>
-        </is>
-      </c>
-      <c r="N242" t="n">
-        <v>1</v>
-      </c>
-      <c r="O242" t="n">
-        <v>1</v>
-      </c>
-      <c r="U242" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
-      <c r="AA242" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AO242" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP242" t="inlineStr">
-        <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS242" t="inlineStr">
-        <is>
-          <t>HOLD_DE_fb64b5712861b2bd0397da7f1dac</t>
-        </is>
-      </c>
-      <c r="AT242" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV242" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="AW242" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="AX242" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="AY242" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="AZ242" t="inlineStr">
-        <is>
-          <t>rki_survstat</t>
-        </is>
-      </c>
-      <c r="BA242" t="inlineStr">
-        <is>
-          <t>Germany RKI SurvStat 2.0</t>
-        </is>
-      </c>
-      <c r="BB242" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
-        </is>
-      </c>
-      <c r="BC242" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -35250,7 +34503,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -35270,7 +34523,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -35280,7 +34533,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
